--- a/RF_test01_Results.xlsx
+++ b/RF_test01_Results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,11 @@
           <t>總耗時(ms)</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>測試時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -465,13 +470,18 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.07000000000000001</v>
+        <v>54.27</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>54.27</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>54.27</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35:08</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -491,13 +501,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.05</v>
+        <v>111.47</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>111.47</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>111.47</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35:09</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -517,13 +532,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>54.38</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>103.49</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>103.49</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35:11</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -543,13 +563,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>108.55</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>108.55</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>108.55</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35:12</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -569,13 +594,18 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>112.14</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>112.14</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>112.14</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35:13</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -595,13 +625,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>111.37</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>111.37</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>111.37</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35:15</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -621,13 +656,18 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.09</v>
+        <v>111.14</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>111.14</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>111.14</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35:16</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -647,13 +687,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>110.96</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>110.96</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>110.96</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35:17</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -673,13 +718,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.08</v>
+        <v>111.23</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>111.23</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>111.23</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35:19</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -699,13 +749,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.07000000000000001</v>
+        <v>108.29</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>108.29</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>108.29</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35:20</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -725,13 +780,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>134.11</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>134.11</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35:21</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -751,13 +811,18 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>111.3</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>111.3</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>111.3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35:22</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -777,13 +842,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>54.4</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>103.03</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>103.03</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35:24</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -803,13 +873,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>109.82</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>109.82</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>109.82</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35:25</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -829,13 +904,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.08</v>
+        <v>108.94</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>108.94</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>108.94</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35:26</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -855,429 +935,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>111.93</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>111.93</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>第 1 輪</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>第 1 步</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CheckBox28_1</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>第 1 輪</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>第 2 步</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>CheckBox28_2</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>第 1 輪</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>第 3 步</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>CheckBox28_3</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>第 1 輪</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>第 4 步</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CheckBox28_4</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>第 1 輪</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>第 5 步</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CheckBox28_5</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>第 1 輪</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>第 6 步</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CheckBox28_6</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>第 1 輪</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>第 7 步</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CheckBox28_7</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>第 1 輪</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>第 8 步</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CheckBox28_8</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>第 2 輪</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>第 1 步</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CheckBox28_1</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>第 2 輪</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>第 2 步</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CheckBox28_2</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>第 2 輪</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>第 3 步</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CheckBox28_3</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>第 2 輪</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>第 4 步</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CheckBox28_4</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>第 2 輪</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>第 5 步</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CheckBox28_5</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>第 2 輪</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>第 6 步</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CheckBox28_6</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>第 2 輪</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>第 7 步</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CheckBox28_7</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>第 2 輪</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>第 8 步</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CheckBox28_8</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
+        <v>111.93</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:35:28</t>
+        </is>
       </c>
     </row>
   </sheetData>
